--- a/premise/data/additional_inventories/lci-steel.xlsx
+++ b/premise/data/additional_inventories/lci-steel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D46C92B-6196-9A47-96D6-E36A4FE91668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBB2BFD-47BF-8243-963E-C3654FBEA17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" tabRatio="900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8645" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8654" uniqueCount="490">
   <si>
     <t>Database</t>
   </si>
@@ -5915,6 +5915,15 @@
       <c r="I13" t="s">
         <v>205</v>
       </c>
+      <c r="O13" t="s">
+        <v>397</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -10507,6 +10516,15 @@
       <c r="I13" t="s">
         <v>205</v>
       </c>
+      <c r="O13" t="s">
+        <v>397</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="14" spans="1:17" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -14702,6 +14720,15 @@
       </c>
       <c r="I13" t="s">
         <v>205</v>
+      </c>
+      <c r="O13" t="s">
+        <v>397</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
